--- a/TestData/Excel_data/Stratos_Test_Data.xlsx
+++ b/TestData/Excel_data/Stratos_Test_Data.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{7400ACE0-2457-410B-842B-BF0B83CFB2F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{9908E085-D82E-4262-8C5E-335B283A6ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="19460" windowHeight="11060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="19460" windowHeight="11060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LOGIN" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
     <sheet name="Manager Data" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:J17"/>
+  <oleSize ref="A1:H17"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -397,15 +397,6 @@
     <t>Windows fitting in 6th floor</t>
   </si>
   <si>
-    <t>delamanagerone@gmail.com</t>
-  </si>
-  <si>
-    <t>delasupervisorone@gmail.com</t>
-  </si>
-  <si>
-    <t>delaemployeeone@gmail.com</t>
-  </si>
-  <si>
     <t>Task Name</t>
   </si>
   <si>
@@ -436,15 +427,6 @@
     <t>Fitting windows</t>
   </si>
   <si>
-    <t>Dela Manager One</t>
-  </si>
-  <si>
-    <t>Dela Supervisor One</t>
-  </si>
-  <si>
-    <t>Dela Employee One</t>
-  </si>
-  <si>
     <t>sampleprovider01 pvt ltd</t>
   </si>
   <si>
@@ -466,10 +448,28 @@
     <t>Zina</t>
   </si>
   <si>
-    <t>maranmara003@gmail.com</t>
-  </si>
-  <si>
-    <t>86547</t>
+    <t>RAMU1</t>
+  </si>
+  <si>
+    <t>maranmara006@gmail.com</t>
+  </si>
+  <si>
+    <t>Dela Manager Two</t>
+  </si>
+  <si>
+    <t>Dela Supervisor Two</t>
+  </si>
+  <si>
+    <t>Dela Employee Two</t>
+  </si>
+  <si>
+    <t>delamanagertwo@gmail.com</t>
+  </si>
+  <si>
+    <t>delasupervisortwo@gmail.com</t>
+  </si>
+  <si>
+    <t>delaemployeetwo@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -603,13 +603,13 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -918,8 +918,8 @@
       <c r="B2">
         <v>123456</v>
       </c>
-      <c r="C2" s="27" t="s">
-        <v>147</v>
+      <c r="C2" s="25" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -997,7 +997,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B2" s="3">
         <v>9984738816</v>
@@ -1006,7 +1006,7 @@
         <v>8972736635</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E2" s="3">
         <v>7782937352</v>
@@ -1030,7 +1030,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B3" s="3">
         <v>8873635363</v>
@@ -1039,7 +1039,7 @@
         <v>7723627463</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E3" s="3">
         <v>9036384763</v>
@@ -1105,16 +1105,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C2">
         <v>99876352163</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E2">
         <v>9987635263</v>
@@ -1226,79 +1226,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:55" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25" t="s">
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25" t="s">
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="Y1" s="25"/>
-      <c r="Z1" s="25"/>
-      <c r="AA1" s="25"/>
-      <c r="AB1" s="25"/>
-      <c r="AC1" s="25"/>
-      <c r="AD1" s="25"/>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="25"/>
-      <c r="AH1" s="25" t="s">
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="26"/>
+      <c r="AB1" s="26"/>
+      <c r="AC1" s="26"/>
+      <c r="AD1" s="26"/>
+      <c r="AE1" s="26"/>
+      <c r="AF1" s="26"/>
+      <c r="AG1" s="26"/>
+      <c r="AH1" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="AI1" s="25"/>
-      <c r="AJ1" s="25"/>
-      <c r="AK1" s="25"/>
-      <c r="AL1" s="25" t="s">
+      <c r="AI1" s="26"/>
+      <c r="AJ1" s="26"/>
+      <c r="AK1" s="26"/>
+      <c r="AL1" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="AM1" s="25"/>
-      <c r="AN1" s="25" t="s">
+      <c r="AM1" s="26"/>
+      <c r="AN1" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="AO1" s="25"/>
-      <c r="AP1" s="25" t="s">
+      <c r="AO1" s="26"/>
+      <c r="AP1" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="AQ1" s="25"/>
-      <c r="AR1" s="25"/>
-      <c r="AS1" s="25"/>
-      <c r="AT1" s="26" t="s">
+      <c r="AQ1" s="26"/>
+      <c r="AR1" s="26"/>
+      <c r="AS1" s="26"/>
+      <c r="AT1" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="AU1" s="26"/>
-      <c r="AV1" s="26"/>
-      <c r="AW1" s="26"/>
-      <c r="AX1" s="26"/>
-      <c r="AY1" s="26" t="s">
+      <c r="AU1" s="27"/>
+      <c r="AV1" s="27"/>
+      <c r="AW1" s="27"/>
+      <c r="AX1" s="27"/>
+      <c r="AY1" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="AZ1" s="26"/>
-      <c r="BA1" s="26"/>
+      <c r="AZ1" s="27"/>
+      <c r="BA1" s="27"/>
       <c r="BB1" s="19" t="s">
         <v>90</v>
       </c>
@@ -1475,7 +1475,7 @@
     </row>
     <row r="3" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>31</v>
@@ -1487,7 +1487,7 @@
         <v>8826373625</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>31</v>
@@ -1625,7 +1625,7 @@
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>32</v>
@@ -1637,7 +1637,7 @@
         <v>6382638273</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>32</v>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>33</v>
@@ -1786,7 +1786,7 @@
         <v>9028372882</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>33</v>
@@ -1990,45 +1990,45 @@
         <v>121</v>
       </c>
       <c r="D1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1" t="s">
         <v>127</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J1" t="s">
         <v>130</v>
       </c>
-      <c r="G1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>131</v>
-      </c>
-      <c r="I1" t="s">
-        <v>131</v>
-      </c>
-      <c r="J1" t="s">
-        <v>133</v>
-      </c>
-      <c r="K1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
         <v>122</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F2">
         <v>11</v>
